--- a/data/memories/memory_01/locales/es/documents/reception/Reception_Log_Current.xlsx
+++ b/data/memories/memory_01/locales/es/documents/reception/Reception_Log_Current.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Reception Log Current</t>
+          <t>Registro de recepción actual</t>
         </is>
       </c>
     </row>
@@ -445,7 +445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -469,33 +469,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reception</t>
+          <t>Recepción</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Current Reception Log</t>
+          <t>Registro de recepción actual</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Current daily reception activity log.</t>
+          <t>Registro diario de actividad de recepción actual.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Tiempo</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Evento</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Entrega</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Candidate interview</t>
+          <t>Entrevista al candidato</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Management meeting</t>
+          <t>reunión de gestión</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Archive inventory</t>
+          <t>Inventario de archivo</t>
         </is>
       </c>
     </row>
